--- a/DemoWebShop/src/test/resources/TestData.xlsx
+++ b/DemoWebShop/src/test/resources/TestData.xlsx
@@ -3,12 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\eclipse-workspace\DemoWebShop\src\test\resources\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C987B3-801A-48B9-B96B-AE1EA2DD35E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{35B59B37-30F7-4EEA-ADF3-DE7100380C08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{A30DB62C-1296-48AC-836F-ADC6C3B2B000}"/>
   </bookViews>
@@ -23,6 +18,7 @@
     <sheet name="GiftCards_Data" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -32,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="404">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -1223,12 +1219,36 @@
   </si>
   <si>
     <t>Display-12</t>
+  </si>
+  <si>
+    <t>RahulRahulRahulRahulRahulRahulRahulRahulRahulRahul</t>
+  </si>
+  <si>
+    <t>NaikNaikNaikNaikNaikNaikNaikNaikNaikNaik</t>
+  </si>
+  <si>
+    <t>rahulnaikmax@gmail.com</t>
+  </si>
+  <si>
+    <t>TestCompanyTestCompanyTestCompanyTestCompanyTestCompany</t>
+  </si>
+  <si>
+    <t>BengaluruBengaluruBengaluruBengaluruBengaluru</t>
+  </si>
+  <si>
+    <t>BillingAddressBillingAddressBillingAddressBillingAddressBillingAddress</t>
+  </si>
+  <si>
+    <t>Address2Address2Address2Address2Address2Address2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0;[Red]0"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1278,7 +1298,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1312,6 +1332,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3268,7 +3294,8 @@
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="5" max="5" width="18.33203125" customWidth="1"/>
     <col min="10" max="10" width="18.88671875" customWidth="1"/>
-    <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="21.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -4170,18 +4197,42 @@
       <c r="B19" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
+      <c r="C19" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="L19" s="12">
+        <v>5.6000156000156E+17</v>
+      </c>
+      <c r="M19" s="13">
+        <v>9.8765432109876494E+19</v>
+      </c>
+      <c r="N19" s="13">
+        <v>9.8765432109876494E+19</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" s="2" t="s">
         <v>31</v>

--- a/DemoWebShop/src/test/resources/TestData.xlsx
+++ b/DemoWebShop/src/test/resources/TestData.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{35B59B37-30F7-4EEA-ADF3-DE7100380C08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{165CCE6A-78E8-46D1-82F6-147944DF6CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{A30DB62C-1296-48AC-836F-ADC6C3B2B000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{A30DB62C-1296-48AC-836F-ADC6C3B2B000}"/>
   </bookViews>
   <sheets>
     <sheet name="Register_Data" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="GiftCards_Data" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
+  <oleSize ref="A1:S6"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
